--- a/03-valuation/Valuation_Model_Astral_School.xlsx
+++ b/03-valuation/Valuation_Model_Astral_School.xlsx
@@ -5001,13 +5001,16 @@
       <c r="B55" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="C55" s="10" t="n">
+      <c r="C55" s="10">
+        <f>(NPV($B55,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B55-Assumptions!$C$10))/(1+$B55)^6-'Audited Base'!$C$37)/100000</f>
         <v>374.3478715007848</v>
       </c>
-      <c r="D55" s="10" t="n">
+      <c r="D55" s="10">
+        <f>(NPV($B55,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B55-Assumptions!$C$10))/(1+$B55)^6-'Audited Base'!$C$37)/100000</f>
         <v>681.4881821843841</v>
       </c>
-      <c r="E55" s="10" t="n">
+      <c r="E55" s="10">
+        <f>(NPV($B55,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B55-Assumptions!$C$10))/(1+$B55)^6-'Audited Base'!$C$37)/100000</f>
         <v>965.800285823213</v>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -5020,13 +5023,16 @@
       <c r="B56" s="41" t="n">
         <v>0.14</v>
       </c>
-      <c r="C56" s="10" t="n">
+      <c r="C56" s="10">
+        <f>(NPV($B56,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B56-Assumptions!$C$10))/(1+$B56)^6-'Audited Base'!$C$37)/100000</f>
         <v>133.8565576063081</v>
       </c>
-      <c r="D56" s="10" t="n">
+      <c r="D56" s="10">
+        <f>(NPV($B56,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B56-Assumptions!$C$10))/(1+$B56)^6-'Audited Base'!$C$37)/100000</f>
         <v>288.1115833915733</v>
       </c>
-      <c r="E56" s="10" t="n">
+      <c r="E56" s="10">
+        <f>(NPV($B56,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B56-Assumptions!$C$10))/(1+$B56)^6-'Audited Base'!$C$37)/100000</f>
         <v>431.7502768148422</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
@@ -5035,13 +5041,16 @@
       <c r="B57" s="41" t="n">
         <v>0.16</v>
       </c>
-      <c r="C57" s="10" t="n">
+      <c r="C57" s="10">
+        <f>(NPV($B57,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B57-Assumptions!$C$10))/(1+$B57)^6-'Audited Base'!$C$37)/100000</f>
         <v>79.79707725209288</v>
       </c>
-      <c r="D57" s="10" t="n">
+      <c r="D57" s="10">
+        <f>(NPV($B57,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B57-Assumptions!$C$10))/(1+$B57)^6-'Audited Base'!$C$37)/100000</f>
         <v>200.096640803215</v>
       </c>
-      <c r="E57" s="10" t="n">
+      <c r="E57" s="10">
+        <f>(NPV($B57,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B57-Assumptions!$C$10))/(1+$B57)^6-'Audited Base'!$C$37)/100000</f>
         <v>312.3823670974401</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
@@ -5050,14 +5059,17 @@
       <c r="B58" s="41" t="n">
         <v>0.19</v>
       </c>
-      <c r="C58" s="13" t="n">
-        <v>28.16905374859341</v>
-      </c>
-      <c r="D58" s="13" t="n">
-        <v>116.3892066847429</v>
-      </c>
-      <c r="E58" s="13" t="n">
-        <v>198.967253988027</v>
+      <c r="C58" s="13">
+        <f>(NPV($B58,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B58-Assumptions!$C$10))/(1+$B58)^6-'Audited Base'!$C$37)/100000</f>
+        <v>28.169053748593406</v>
+      </c>
+      <c r="D58" s="13">
+        <f>(NPV($B58,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B58-Assumptions!$C$10))/(1+$B58)^6-'Audited Base'!$C$37)/100000</f>
+        <v>116.38920668474287</v>
+      </c>
+      <c r="E58" s="13">
+        <f>(NPV($B58,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B58-Assumptions!$C$10))/(1+$B58)^6-'Audited Base'!$C$37)/100000</f>
+        <v>198.96725398802698</v>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
@@ -5069,14 +5081,17 @@
       <c r="B59" s="41" t="n">
         <v>0.22</v>
       </c>
-      <c r="C59" s="10" t="n">
+      <c r="C59" s="10">
+        <f>(NPV($B59,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B59-Assumptions!$C$10))/(1+$B59)^6-'Audited Base'!$C$37)/100000</f>
         <v>-4.805191819553096</v>
       </c>
-      <c r="D59" s="10" t="n">
-        <v>63.23037248332314</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>127.0448723839584</v>
+      <c r="D59" s="10">
+        <f>(NPV($B59,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B59-Assumptions!$C$10))/(1+$B59)^6-'Audited Base'!$C$37)/100000</f>
+        <v>63.230372483323144</v>
+      </c>
+      <c r="E59" s="10">
+        <f>(NPV($B59,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B59-Assumptions!$C$10))/(1+$B59)^6-'Audited Base'!$C$37)/100000</f>
+        <v>127.04487238395843</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -5084,13 +5099,16 @@
       <c r="B60" s="41" t="n">
         <v>0.25</v>
       </c>
-      <c r="C60" s="10" t="n">
-        <v>-27.57068399112443</v>
-      </c>
-      <c r="D60" s="10" t="n">
+      <c r="C60" s="10">
+        <f>(NPV($B60,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B60-Assumptions!$C$10))/(1+$B60)^6-'Audited Base'!$C$37)/100000</f>
+        <v>-27.570683991124426</v>
+      </c>
+      <c r="D60" s="10">
+        <f>(NPV($B60,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B60-Assumptions!$C$10))/(1+$B60)^6-'Audited Base'!$C$37)/100000</f>
         <v>26.75524477289753</v>
       </c>
-      <c r="E60" s="10" t="n">
+      <c r="E60" s="10">
+        <f>(NPV($B60,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B60-Assumptions!$C$10))/(1+$B60)^6-'Audited Base'!$C$37)/100000</f>
         <v>77.7760336626985</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
@@ -5602,7 +5620,8 @@
       <c r="B12" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="8">
+        <f>NPV($B12,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B12-Assumptions!$C$10))/(1+$B12)^6-'Audited Base'!$C$37</f>
         <v>96580028.5823213</v>
       </c>
       <c r="D12" s="20">
@@ -5619,7 +5638,8 @@
       <c r="B13" s="41" t="n">
         <v>0.11</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="8">
+        <f>NPV($B13,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B13-Assumptions!$C$10))/(1+$B13)^6-'Audited Base'!$C$37</f>
         <v>76452909.02366123</v>
       </c>
       <c r="D13" s="18">
@@ -5632,8 +5652,9 @@
       <c r="B14" s="41" t="n">
         <v>0.12</v>
       </c>
-      <c r="C14" s="8" t="n">
-        <v>62135683.84624141</v>
+      <c r="C14" s="8">
+        <f>NPV($B14,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B14-Assumptions!$C$10))/(1+$B14)^6-'Audited Base'!$C$37</f>
+        <v>62135683.846241415</v>
       </c>
       <c r="D14" s="18">
         <f>C14/$C$6</f>
@@ -5645,7 +5666,8 @@
       <c r="B15" s="41" t="n">
         <v>0.14</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="8">
+        <f>NPV($B15,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B15-Assumptions!$C$10))/(1+$B15)^6-'Audited Base'!$C$37</f>
         <v>43175027.68148422</v>
       </c>
       <c r="D15" s="18">
@@ -5658,8 +5680,9 @@
       <c r="B16" s="41" t="n">
         <v>0.19</v>
       </c>
-      <c r="C16" s="8" t="n">
-        <v>19896725.3988027</v>
+      <c r="C16" s="8">
+        <f>NPV($B16,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B16-Assumptions!$C$10))/(1+$B16)^6-'Audited Base'!$C$37</f>
+        <v>19896725.398802698</v>
       </c>
       <c r="D16" s="18">
         <f>C16/$C$6</f>

--- a/03-valuation/Valuation_Model_Astral_School.xlsx
+++ b/03-valuation/Valuation_Model_Astral_School.xlsx
@@ -149,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -229,7 +229,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4087,7 +4092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I62"/>
+  <dimension ref="B2:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4124,7 +4129,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
     </row>
-    <row r="6" ht="24" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Risk-free rate (10-year G-sec)</t>
@@ -4135,11 +4140,11 @@
       </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
-          <t>Indicative</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
+          <t>Indian 10-year government security, indicative</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Equity risk premium, India</t>
@@ -4150,11 +4155,11 @@
       </c>
       <c r="I7" s="39" t="inlineStr">
         <is>
-          <t>Market</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
+          <t>Premium investors require over the risk-free rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Beta, education sector</t>
@@ -4165,11 +4170,11 @@
       </c>
       <c r="I8" s="39" t="inlineStr">
         <is>
-          <t>Unlevered, sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
+          <t>Sector beta, unlevered</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Size and illiquidity premium</t>
@@ -4180,11 +4185,11 @@
       </c>
       <c r="I9" s="39" t="inlineStr">
         <is>
-          <t>Unlisted, single site, no market for the shares</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
+          <t>Unlisted micro-cap; there is no market in which to sell these shares</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
       <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Company-specific risk premium</t>
@@ -4195,26 +4200,27 @@
       </c>
       <c r="I10" s="39" t="inlineStr">
         <is>
-          <t>One campus, leased land, Board permission not yet obtained, key-person dependence</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="33" t="inlineStr">
-        <is>
-          <t>Cost of equity</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="I11" s="39" t="inlineStr">
-        <is>
-          <t>Risk-free + beta × ERP + premiums</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
+          <t>One campus, leased land, Maharashtra Board permission not yet obtained, key-person dependence, first year of audited accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="45" t="inlineStr">
+        <is>
+          <t>COST OF EQUITY</t>
+        </is>
+      </c>
+      <c r="C11" s="46">
+        <f>C6+C8*C7+C9+C10</f>
+        <v>0.255</v>
+      </c>
+      <c r="I11" s="47" t="inlineStr">
+        <is>
+          <t>Risk-free + (beta × equity risk premium) + premiums</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt</t>
@@ -4225,26 +4231,27 @@
       </c>
       <c r="I12" s="39" t="inlineStr">
         <is>
-          <t>Rate on existing loans per Raw-Data sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
+          <t>Rate on the company’s existing loans per the Raw-Data sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="C13" s="36" t="n">
+      <c r="C13" s="36">
+        <f>C12*(1-Assumptions!$C$8)</f>
         <v>0.074</v>
       </c>
       <c r="I13" s="39" t="inlineStr">
         <is>
-          <t>× (1 − tax rate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
+          <t>Interest is tax deductible</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Target equity weighting</t>
@@ -4255,866 +4262,899 @@
       </c>
       <c r="I14" s="39" t="inlineStr">
         <is>
-          <t>Post-transaction</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>WACC — rounded and used throughout</t>
-        </is>
-      </c>
-      <c r="C15" s="45" t="n">
+          <t>Post-transaction capital structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Target debt weighting</t>
+        </is>
+      </c>
+      <c r="C15" s="36">
+        <f>1-C14</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="I15" s="39" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>WACC — CALCULATED</t>
+        </is>
+      </c>
+      <c r="C16" s="48">
+        <f>C14*C11+C15*C13</f>
+        <v>0.2007</v>
+      </c>
+      <c r="I16" s="49" t="inlineStr">
+        <is>
+          <t>Equity weight × cost of equity + debt weight × after-tax cost of debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>WACC — APPLIED throughout this model</t>
+        </is>
+      </c>
+      <c r="C17" s="48">
+        <f>Assumptions!$C$9</f>
         <v>0.19</v>
       </c>
-      <c r="I15" s="46" t="inlineStr">
-        <is>
-          <t>Entered on the Assumptions tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="I17" s="49" t="inlineStr">
+        <is>
+          <t>Rounded DOWN from the calculated rate, deliberately and in management’s favour: a lower discount rate produces a HIGHER valuation. Change it on the Assumptions tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>CASE A — ORGANIC (NO NEW CAPITAL)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="37" t="inlineStr">
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>₹</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>2026-27</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>2027-28</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>2028-29</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>2029-30</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>2030-31</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>2031-32</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="5" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="C19" s="6">
+      <c r="C21" s="6">
         <f>Projections!C22</f>
         <v>1457394.9411354838</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D21" s="6">
         <f>Projections!D22</f>
         <v>1800036.5123852259</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E21" s="6">
         <f>Projections!E22</f>
         <v>2137609.3470367165</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F21" s="6">
         <f>Projections!F22</f>
         <v>2528627.8673981708</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G21" s="6">
         <f>Projections!G22</f>
         <v>2915679.403183006</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H21" s="6">
         <f>Projections!H22</f>
         <v>3491581.111479815</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C20" s="47">
+      <c r="C22" s="50">
         <f>1/(1+Assumptions!$C$9)^1</f>
         <v>0.8403361344537815</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D22" s="50">
         <f>1/(1+Assumptions!$C$9)^2</f>
         <v>0.706164818868724</v>
       </c>
-      <c r="E20" s="47">
+      <c r="E22" s="50">
         <f>1/(1+Assumptions!$C$9)^3</f>
         <v>0.5934158141753983</v>
       </c>
-      <c r="F20" s="47">
+      <c r="F22" s="50">
         <f>1/(1+Assumptions!$C$9)^4</f>
         <v>0.4986687514078978</v>
       </c>
-      <c r="G20" s="47">
+      <c r="G22" s="50">
         <f>1/(1+Assumptions!$C$9)^5</f>
         <v>0.41904937093100664</v>
       </c>
-      <c r="H20" s="47">
+      <c r="H22" s="50">
         <f>1/(1+Assumptions!$C$9)^6</f>
         <v>0.3521423285134509</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>Present value of cash flow</t>
-        </is>
-      </c>
-      <c r="C21" s="34">
-        <f>C19*C20</f>
-        <v>1224701.631206289</v>
-      </c>
-      <c r="D21" s="34">
-        <f>D19*D20</f>
-        <v>1271122.4577256027</v>
-      </c>
-      <c r="E21" s="34">
-        <f>E19*E20</f>
-        <v>1268491.1910607347</v>
-      </c>
-      <c r="F21" s="34">
-        <f>F19*F20</f>
-        <v>1260947.7014106612</v>
-      </c>
-      <c r="G21" s="34">
-        <f>G19*G20</f>
-        <v>1221813.6197403315</v>
-      </c>
-      <c r="H21" s="34">
-        <f>H19*H20</f>
-        <v>1229533.502790085</v>
-      </c>
-      <c r="I21" s="25">
-        <f>SUM(C21:H21)</f>
-        <v>7476610.103933704</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Terminal value at end of FY32</t>
-        </is>
-      </c>
-      <c r="C22" s="8">
-        <f>H19*(1+Assumptions!$C$10)/(Assumptions!$C$9-Assumptions!$C$10)</f>
-        <v>26186858.33609861</v>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Gordon growth</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
       <c r="B23" s="33" t="inlineStr">
         <is>
+          <t>Present value of cash flow</t>
+        </is>
+      </c>
+      <c r="C23" s="34">
+        <f>C21*C22</f>
+        <v>1224701.631206289</v>
+      </c>
+      <c r="D23" s="34">
+        <f>D21*D22</f>
+        <v>1271122.4577256027</v>
+      </c>
+      <c r="E23" s="34">
+        <f>E21*E22</f>
+        <v>1268491.1910607347</v>
+      </c>
+      <c r="F23" s="34">
+        <f>F21*F22</f>
+        <v>1260947.7014106612</v>
+      </c>
+      <c r="G23" s="34">
+        <f>G21*G22</f>
+        <v>1221813.6197403315</v>
+      </c>
+      <c r="H23" s="34">
+        <f>H21*H22</f>
+        <v>1229533.502790085</v>
+      </c>
+      <c r="I23" s="25">
+        <f>SUM(C23:H23)</f>
+        <v>7476610.103933704</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Terminal value at end of FY32</t>
+        </is>
+      </c>
+      <c r="C24" s="8">
+        <f>H21*(1+Assumptions!$C$10)/(Assumptions!$C$9-Assumptions!$C$10)</f>
+        <v>26186858.33609861</v>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Gordon growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="33" t="inlineStr">
+        <is>
           <t>Present value of terminal value</t>
         </is>
       </c>
-      <c r="C23" s="34">
-        <f>C22*H20</f>
+      <c r="C25" s="34">
+        <f>C24*H22</f>
         <v>9221501.270925637</v>
       </c>
-      <c r="I23" s="25">
-        <f>C23</f>
+      <c r="I25" s="25">
+        <f>C25</f>
         <v>9221501.270925637</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="12" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="I24" s="28">
-        <f>$I$21+$I$23</f>
+      <c r="I26" s="28">
+        <f>$I$23+$I$25</f>
         <v>16698111.37485934</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="5" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Less net debt</t>
         </is>
       </c>
-      <c r="I25" s="6">
+      <c r="I27" s="6">
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="12" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>EQUITY VALUE</t>
         </is>
       </c>
-      <c r="I26" s="28">
-        <f>$I$24-'Audited Base'!$C$37</f>
+      <c r="I28" s="28">
+        <f>$I$26-'Audited Base'!$C$37</f>
         <v>2816905.3748593405</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Terminal value as % of enterprise value</t>
         </is>
       </c>
-      <c r="I27" s="43">
-        <f>$I$23/$I$24</f>
+      <c r="I29" s="43">
+        <f>$I$25/$I$26</f>
         <v>0.5522481593223483</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>CASE B — MANAGEMENT CONSERVATIVE</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="37" t="inlineStr">
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="37" t="inlineStr">
         <is>
           <t>₹</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>2026-27</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>2027-28</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>2028-29</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>2029-30</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>2030-31</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>2031-32</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="5" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="C31" s="6">
+      <c r="C33" s="6">
         <f>Projections!C41</f>
         <v>1571257.8327741937</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D33" s="6">
         <f>Projections!D41</f>
         <v>2214800.595796774</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E33" s="6">
         <f>Projections!E41</f>
         <v>2915494.6840056404</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F33" s="6">
         <f>Projections!F41</f>
         <v>3612484.646204727</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G33" s="6">
         <f>Projections!G41</f>
         <v>4605500.820200572</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H33" s="6">
         <f>Projections!H41</f>
         <v>5737740.6809697235</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C32" s="47">
+      <c r="C34" s="50">
         <f>1/(1+Assumptions!$C$9)^1</f>
         <v>0.8403361344537815</v>
       </c>
-      <c r="D32" s="47">
+      <c r="D34" s="50">
         <f>1/(1+Assumptions!$C$9)^2</f>
         <v>0.706164818868724</v>
       </c>
-      <c r="E32" s="47">
+      <c r="E34" s="50">
         <f>1/(1+Assumptions!$C$9)^3</f>
         <v>0.5934158141753983</v>
       </c>
-      <c r="F32" s="47">
+      <c r="F34" s="50">
         <f>1/(1+Assumptions!$C$9)^4</f>
         <v>0.4986687514078978</v>
       </c>
-      <c r="G32" s="47">
+      <c r="G34" s="50">
         <f>1/(1+Assumptions!$C$9)^5</f>
         <v>0.41904937093100664</v>
       </c>
-      <c r="H32" s="47">
+      <c r="H34" s="50">
         <f>1/(1+Assumptions!$C$9)^6</f>
         <v>0.3521423285134509</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>Present value of cash flow</t>
-        </is>
-      </c>
-      <c r="C33" s="34">
-        <f>C31*C32</f>
-        <v>1320384.7334236922</v>
-      </c>
-      <c r="D33" s="34">
-        <f>D31*D32</f>
-        <v>1564014.261561171</v>
-      </c>
-      <c r="E33" s="34">
-        <f>E31*E32</f>
-        <v>1730100.6516332529</v>
-      </c>
-      <c r="F33" s="34">
-        <f>F31*F32</f>
-        <v>1801433.2080031126</v>
-      </c>
-      <c r="G33" s="34">
-        <f>G31*G32</f>
-        <v>1929932.2215272847</v>
-      </c>
-      <c r="H33" s="34">
-        <f>H31*H32</f>
-        <v>2020501.3638030319</v>
-      </c>
-      <c r="I33" s="25">
-        <f>SUM(C33:H33)</f>
-        <v>10366366.439951546</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Terminal value at end of FY32</t>
-        </is>
-      </c>
-      <c r="C34" s="8">
-        <f>H31*(1+Assumptions!$C$10)/(Assumptions!$C$9-Assumptions!$C$10)</f>
-        <v>43033055.10727292</v>
-      </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>Gordon growth</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
       <c r="B35" s="33" t="inlineStr">
         <is>
+          <t>Present value of cash flow</t>
+        </is>
+      </c>
+      <c r="C35" s="34">
+        <f>C33*C34</f>
+        <v>1320384.7334236922</v>
+      </c>
+      <c r="D35" s="34">
+        <f>D33*D34</f>
+        <v>1564014.261561171</v>
+      </c>
+      <c r="E35" s="34">
+        <f>E33*E34</f>
+        <v>1730100.6516332529</v>
+      </c>
+      <c r="F35" s="34">
+        <f>F33*F34</f>
+        <v>1801433.2080031126</v>
+      </c>
+      <c r="G35" s="34">
+        <f>G33*G34</f>
+        <v>1929932.2215272847</v>
+      </c>
+      <c r="H35" s="34">
+        <f>H33*H34</f>
+        <v>2020501.3638030319</v>
+      </c>
+      <c r="I35" s="25">
+        <f>SUM(C35:H35)</f>
+        <v>10366366.439951546</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Terminal value at end of FY32</t>
+        </is>
+      </c>
+      <c r="C36" s="8">
+        <f>H33*(1+Assumptions!$C$10)/(Assumptions!$C$9-Assumptions!$C$10)</f>
+        <v>43033055.10727292</v>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Gordon growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="33" t="inlineStr">
+        <is>
           <t>Present value of terminal value</t>
         </is>
       </c>
-      <c r="C35" s="34">
-        <f>C34*H32</f>
+      <c r="C37" s="34">
+        <f>C36*H34</f>
         <v>15153760.228522738</v>
       </c>
-      <c r="I35" s="25">
-        <f>C35</f>
+      <c r="I37" s="25">
+        <f>C37</f>
         <v>15153760.228522738</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="12" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="I36" s="28">
-        <f>$I$33+$I$35</f>
+      <c r="I38" s="28">
+        <f>$I$35+$I$37</f>
         <v>25520126.668474287</v>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="5" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Less net debt</t>
         </is>
       </c>
-      <c r="I37" s="6">
+      <c r="I39" s="6">
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="12" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>EQUITY VALUE</t>
         </is>
       </c>
-      <c r="I38" s="28">
-        <f>$I$36-'Audited Base'!$C$37</f>
+      <c r="I40" s="28">
+        <f>$I$38-'Audited Base'!$C$37</f>
         <v>11638920.668474287</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Terminal value as % of enterprise value</t>
         </is>
       </c>
-      <c r="I39" s="43">
-        <f>$I$35/$I$36</f>
+      <c r="I41" s="43">
+        <f>$I$37/$I$38</f>
         <v>0.5937964346878651</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="3" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>CASE C — MANAGEMENT MODERATE</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="B42" s="37" t="inlineStr">
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="37" t="inlineStr">
         <is>
           <t>₹</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>2026-27</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>2027-28</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>2028-29</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2029-30</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>2030-31</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>2031-32</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="5" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="C43" s="6">
+      <c r="C45" s="6">
         <f>Projections!C60</f>
         <v>1571257.8327741937</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D45" s="6">
         <f>Projections!D60</f>
         <v>2511060.655376452</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E45" s="6">
         <f>Projections!E60</f>
         <v>3693380.0209745653</v>
       </c>
-      <c r="F43" s="6">
+      <c r="F45" s="6">
         <f>Projections!F60</f>
         <v>4997412.752457546</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G45" s="6">
         <f>Projections!G60</f>
         <v>6355673.002111619</v>
       </c>
-      <c r="H43" s="6">
+      <c r="H45" s="6">
         <f>Projections!H60</f>
         <v>7796720.286335472</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C44" s="47">
+      <c r="C46" s="50">
         <f>1/(1+Assumptions!$C$9)^1</f>
         <v>0.8403361344537815</v>
       </c>
-      <c r="D44" s="47">
+      <c r="D46" s="50">
         <f>1/(1+Assumptions!$C$9)^2</f>
         <v>0.706164818868724</v>
       </c>
-      <c r="E44" s="47">
+      <c r="E46" s="50">
         <f>1/(1+Assumptions!$C$9)^3</f>
         <v>0.5934158141753983</v>
       </c>
-      <c r="F44" s="47">
+      <c r="F46" s="50">
         <f>1/(1+Assumptions!$C$9)^4</f>
         <v>0.4986687514078978</v>
       </c>
-      <c r="G44" s="47">
+      <c r="G46" s="50">
         <f>1/(1+Assumptions!$C$9)^5</f>
         <v>0.41904937093100664</v>
       </c>
-      <c r="H44" s="47">
+      <c r="H46" s="50">
         <f>1/(1+Assumptions!$C$9)^6</f>
         <v>0.3521423285134509</v>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="33" t="inlineStr">
-        <is>
-          <t>Present value of cash flow</t>
-        </is>
-      </c>
-      <c r="C45" s="34">
-        <f>C43*C44</f>
-        <v>1320384.7334236922</v>
-      </c>
-      <c r="D45" s="34">
-        <f>D43*D44</f>
-        <v>1773222.6928722914</v>
-      </c>
-      <c r="E45" s="34">
-        <f>E43*E44</f>
-        <v>2191710.1122057713</v>
-      </c>
-      <c r="F45" s="34">
-        <f>F43*F44</f>
-        <v>2492053.57753791</v>
-      </c>
-      <c r="G45" s="34">
-        <f>G43*G44</f>
-        <v>2663340.7733780565</v>
-      </c>
-      <c r="H45" s="34">
-        <f>H43*H44</f>
-        <v>2745555.2363982326</v>
-      </c>
-      <c r="I45" s="25">
-        <f>SUM(C45:H45)</f>
-        <v>13186267.125815954</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Terminal value at end of FY32</t>
-        </is>
-      </c>
-      <c r="C46" s="8">
-        <f>H43*(1+Assumptions!$C$10)/(Assumptions!$C$9-Assumptions!$C$10)</f>
-        <v>58475402.147516035</v>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>Gordon growth</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
       <c r="B47" s="33" t="inlineStr">
         <is>
+          <t>Present value of cash flow</t>
+        </is>
+      </c>
+      <c r="C47" s="34">
+        <f>C45*C46</f>
+        <v>1320384.7334236922</v>
+      </c>
+      <c r="D47" s="34">
+        <f>D45*D46</f>
+        <v>1773222.6928722914</v>
+      </c>
+      <c r="E47" s="34">
+        <f>E45*E46</f>
+        <v>2191710.1122057713</v>
+      </c>
+      <c r="F47" s="34">
+        <f>F45*F46</f>
+        <v>2492053.57753791</v>
+      </c>
+      <c r="G47" s="34">
+        <f>G45*G46</f>
+        <v>2663340.7733780565</v>
+      </c>
+      <c r="H47" s="34">
+        <f>H45*H46</f>
+        <v>2745555.2363982326</v>
+      </c>
+      <c r="I47" s="25">
+        <f>SUM(C47:H47)</f>
+        <v>13186267.125815954</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Terminal value at end of FY32</t>
+        </is>
+      </c>
+      <c r="C48" s="8">
+        <f>H45*(1+Assumptions!$C$10)/(Assumptions!$C$9-Assumptions!$C$10)</f>
+        <v>58475402.147516035</v>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>Gordon growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="33" t="inlineStr">
+        <is>
           <t>Present value of terminal value</t>
         </is>
       </c>
-      <c r="C47" s="34">
-        <f>C46*H44</f>
+      <c r="C49" s="34">
+        <f>C48*H46</f>
         <v>20591664.272986744</v>
       </c>
-      <c r="I47" s="25">
-        <f>C47</f>
+      <c r="I49" s="25">
+        <f>C49</f>
         <v>20591664.272986744</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="12" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="I48" s="28">
-        <f>$I$45+$I$47</f>
+      <c r="I50" s="28">
+        <f>$I$47+$I$49</f>
         <v>33777931.3988027</v>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="5" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Less net debt</t>
         </is>
       </c>
-      <c r="I49" s="6">
+      <c r="I51" s="6">
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="12" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>EQUITY VALUE</t>
         </is>
       </c>
-      <c r="I50" s="28">
-        <f>$I$48-'Audited Base'!$C$37</f>
+      <c r="I52" s="28">
+        <f>$I$50-'Audited Base'!$C$37</f>
         <v>19896725.398802698</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Terminal value as % of enterprise value</t>
         </is>
       </c>
-      <c r="I51" s="43">
-        <f>$I$47/$I$48</f>
+      <c r="I53" s="43">
+        <f>$I$49/$I$50</f>
         <v>0.6096188671197503</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="3" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>EQUITY VALUE SENSITIVITY TO THE DISCOUNT RATE  (₹ lakh)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="n"/>
-      <c r="G53" s="3" t="n"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="37" t="inlineStr">
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="37" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>Case A</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Case B</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Case C</t>
         </is>
       </c>
-      <c r="F54" s="37" t="inlineStr">
+      <c r="F56" s="37" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="41" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C55" s="10">
-        <f>(NPV($B55,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B55-Assumptions!$C$10))/(1+$B55)^6-'Audited Base'!$C$37)/100000</f>
-        <v>374.3478715007848</v>
-      </c>
-      <c r="D55" s="10">
-        <f>(NPV($B55,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B55-Assumptions!$C$10))/(1+$B55)^6-'Audited Base'!$C$37)/100000</f>
-        <v>681.4881821843841</v>
-      </c>
-      <c r="E55" s="10">
-        <f>(NPV($B55,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B55-Assumptions!$C$10))/(1+$B55)^6-'Audited Base'!$C$37)/100000</f>
-        <v>965.800285823213</v>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>← would be needed for ₹10 Cr; see Reverse Test</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="41" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="C56" s="10">
-        <f>(NPV($B56,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B56-Assumptions!$C$10))/(1+$B56)^6-'Audited Base'!$C$37)/100000</f>
-        <v>133.8565576063081</v>
-      </c>
-      <c r="D56" s="10">
-        <f>(NPV($B56,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B56-Assumptions!$C$10))/(1+$B56)^6-'Audited Base'!$C$37)/100000</f>
-        <v>288.1115833915733</v>
-      </c>
-      <c r="E56" s="10">
-        <f>(NPV($B56,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B56-Assumptions!$C$10))/(1+$B56)^6-'Audited Base'!$C$37)/100000</f>
-        <v>431.7502768148422</v>
-      </c>
-      <c r="F56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="41" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="C57" s="10">
         <f>(NPV($B57,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B57-Assumptions!$C$10))/(1+$B57)^6-'Audited Base'!$C$37)/100000</f>
-        <v>79.79707725209288</v>
+        <v>374.3478715007848</v>
       </c>
       <c r="D57" s="10">
         <f>(NPV($B57,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B57-Assumptions!$C$10))/(1+$B57)^6-'Audited Base'!$C$37)/100000</f>
-        <v>200.096640803215</v>
+        <v>681.4881821843841</v>
       </c>
       <c r="E57" s="10">
         <f>(NPV($B57,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B57-Assumptions!$C$10))/(1+$B57)^6-'Audited Base'!$C$37)/100000</f>
-        <v>312.3823670974401</v>
-      </c>
-      <c r="F57" s="7" t="inlineStr"/>
+        <v>965.800285823213</v>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>← would be needed for ₹10 Cr; see Reverse Test</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="B58" s="41" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="C58" s="13">
+        <v>0.14</v>
+      </c>
+      <c r="C58" s="10">
         <f>(NPV($B58,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B58-Assumptions!$C$10))/(1+$B58)^6-'Audited Base'!$C$37)/100000</f>
-        <v>28.169053748593406</v>
-      </c>
-      <c r="D58" s="13">
+        <v>133.8565576063081</v>
+      </c>
+      <c r="D58" s="10">
         <f>(NPV($B58,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B58-Assumptions!$C$10))/(1+$B58)^6-'Audited Base'!$C$37)/100000</f>
-        <v>116.38920668474287</v>
-      </c>
-      <c r="E58" s="13">
+        <v>288.1115833915733</v>
+      </c>
+      <c r="E58" s="10">
         <f>(NPV($B58,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B58-Assumptions!$C$10))/(1+$B58)^6-'Audited Base'!$C$37)/100000</f>
-        <v>198.96725398802698</v>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>← rate used</t>
-        </is>
-      </c>
+        <v>431.7502768148422</v>
+      </c>
+      <c r="F58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="41" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="C59" s="10">
         <f>(NPV($B59,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B59-Assumptions!$C$10))/(1+$B59)^6-'Audited Base'!$C$37)/100000</f>
-        <v>-4.805191819553096</v>
+        <v>79.79707725209288</v>
       </c>
       <c r="D59" s="10">
         <f>(NPV($B59,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B59-Assumptions!$C$10))/(1+$B59)^6-'Audited Base'!$C$37)/100000</f>
-        <v>63.230372483323144</v>
+        <v>200.096640803215</v>
       </c>
       <c r="E59" s="10">
         <f>(NPV($B59,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B59-Assumptions!$C$10))/(1+$B59)^6-'Audited Base'!$C$37)/100000</f>
-        <v>127.04487238395843</v>
+        <v>312.3823670974401</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="41" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C60" s="13">
+        <f>(NPV($B60,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B60-Assumptions!$C$10))/(1+$B60)^6-'Audited Base'!$C$37)/100000</f>
+        <v>28.169053748593406</v>
+      </c>
+      <c r="D60" s="13">
+        <f>(NPV($B60,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B60-Assumptions!$C$10))/(1+$B60)^6-'Audited Base'!$C$37)/100000</f>
+        <v>116.38920668474287</v>
+      </c>
+      <c r="E60" s="13">
+        <f>(NPV($B60,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B60-Assumptions!$C$10))/(1+$B60)^6-'Audited Base'!$C$37)/100000</f>
+        <v>198.96725398802698</v>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>← rate used</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="41" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C61" s="10">
+        <f>(NPV($B61,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B61-Assumptions!$C$10))/(1+$B61)^6-'Audited Base'!$C$37)/100000</f>
+        <v>-4.805191819553096</v>
+      </c>
+      <c r="D61" s="10">
+        <f>(NPV($B61,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B61-Assumptions!$C$10))/(1+$B61)^6-'Audited Base'!$C$37)/100000</f>
+        <v>63.230372483323144</v>
+      </c>
+      <c r="E61" s="10">
+        <f>(NPV($B61,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B61-Assumptions!$C$10))/(1+$B61)^6-'Audited Base'!$C$37)/100000</f>
+        <v>127.04487238395843</v>
+      </c>
+      <c r="F61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="41" t="n">
         <v>0.25</v>
       </c>
-      <c r="C60" s="10">
-        <f>(NPV($B60,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B60-Assumptions!$C$10))/(1+$B60)^6-'Audited Base'!$C$37)/100000</f>
+      <c r="C62" s="10">
+        <f>(NPV($B62,Projections!$C$22:$H$22)+(Projections!$H$22*(1+Assumptions!$C$10)/($B62-Assumptions!$C$10))/(1+$B62)^6-'Audited Base'!$C$37)/100000</f>
         <v>-27.570683991124426</v>
       </c>
-      <c r="D60" s="10">
-        <f>(NPV($B60,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B60-Assumptions!$C$10))/(1+$B60)^6-'Audited Base'!$C$37)/100000</f>
+      <c r="D62" s="10">
+        <f>(NPV($B62,Projections!$C$41:$H$41)+(Projections!$H$41*(1+Assumptions!$C$10)/($B62-Assumptions!$C$10))/(1+$B62)^6-'Audited Base'!$C$37)/100000</f>
         <v>26.75524477289753</v>
       </c>
-      <c r="E60" s="10">
-        <f>(NPV($B60,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B60-Assumptions!$C$10))/(1+$B60)^6-'Audited Base'!$C$37)/100000</f>
+      <c r="E62" s="10">
+        <f>(NPV($B62,Projections!$C$60:$H$60)+(Projections!$H$60*(1+Assumptions!$C$10)/($B62-Assumptions!$C$10))/(1+$B62)^6-'Audited Base'!$C$37)/100000</f>
         <v>77.7760336626985</v>
       </c>
-      <c r="F60" s="7" t="inlineStr"/>
-    </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="B62" s="21" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr"/>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="B64" s="21" t="inlineStr">
         <is>
           <t>The terminal value carries more than half of the enterprise value in every case, which is normal for a growing business but means the conclusion is sensitive to the discount rate and the terminal growth rate. That sensitivity is the point of the table above.</t>
         </is>
@@ -5122,7 +5162,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="B64:I64"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5198,7 +5238,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="48" t="n">
+      <c r="B7" s="51" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="8">
@@ -5209,7 +5249,7 @@
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="52">
         <f>C7+D7</f>
         <v>-1699406</v>
       </c>
@@ -5220,7 +5260,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="48" t="n">
+      <c r="B8" s="51" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="8">
@@ -5231,7 +5271,7 @@
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="52">
         <f>C8+D8</f>
         <v>4391494</v>
       </c>
@@ -5242,7 +5282,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="48" t="n">
+      <c r="B9" s="51" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="8">
@@ -5253,7 +5293,7 @@
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="52">
         <f>C9+D9</f>
         <v>10482394</v>
       </c>
@@ -5264,7 +5304,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="48" t="n">
+      <c r="B10" s="51" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="8">
@@ -5275,7 +5315,7 @@
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="52">
         <f>C10+D10</f>
         <v>16573294</v>
       </c>
@@ -5286,7 +5326,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="48" t="n">
+      <c r="B11" s="51" t="n">
         <v>16.4</v>
       </c>
       <c r="C11" s="8">
@@ -5297,7 +5337,7 @@
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="53">
         <f>C11+D11</f>
         <v>86009553.99999999</v>
       </c>
@@ -5346,7 +5386,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="48" t="n">
+      <c r="B15" s="51" t="n">
         <v>8</v>
       </c>
       <c r="C15" s="8">
@@ -5357,7 +5397,7 @@
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="52">
         <f>C15+D15</f>
         <v>4312554</v>
       </c>
@@ -5368,7 +5408,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="48" t="n">
+      <c r="B16" s="51" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="8">
@@ -5379,7 +5419,7 @@
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="52">
         <f>C16+D16</f>
         <v>8860994</v>
       </c>
@@ -5390,7 +5430,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="48" t="n">
+      <c r="B17" s="51" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="8">
@@ -5401,7 +5441,7 @@
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="52">
         <f>C17+D17</f>
         <v>13409434</v>
       </c>
@@ -5412,7 +5452,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="48" t="n">
+      <c r="B18" s="51" t="n">
         <v>15</v>
       </c>
       <c r="C18" s="8">
@@ -5423,7 +5463,7 @@
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="52">
         <f>C18+D18</f>
         <v>20232094</v>
       </c>
@@ -5434,7 +5474,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="48" t="n">
+      <c r="B19" s="51" t="n">
         <v>50.1</v>
       </c>
       <c r="C19" s="8">
@@ -5445,7 +5485,7 @@
         <f>-'Audited Base'!$C$37</f>
         <v>-13881206</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="53">
         <f>C19+D19</f>
         <v>100057216</v>
       </c>
@@ -5736,7 +5776,7 @@
           <t>Scale-up factor required</t>
         </is>
       </c>
-      <c r="C23" s="51" t="n">
+      <c r="C23" s="54" t="n">
         <v>3.371467738963928</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -5766,7 +5806,7 @@
           <t>Implied FY32 student count</t>
         </is>
       </c>
-      <c r="C25" s="52" t="n">
+      <c r="C25" s="55" t="n">
         <v>2376.884755969569</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -5820,7 +5860,7 @@
         <f>'Audited Base'!$C$7</f>
         <v>6090900</v>
       </c>
-      <c r="D31" s="53">
+      <c r="D31" s="56">
         <f>$C$6/C31</f>
         <v>16.41793495214172</v>
       </c>
@@ -5835,7 +5875,7 @@
         <f>'Audited Base'!$C$25</f>
         <v>2274220</v>
       </c>
-      <c r="D32" s="53">
+      <c r="D32" s="56">
         <f>$C$6/C32</f>
         <v>43.97111976853603</v>
       </c>
@@ -5849,7 +5889,7 @@
       <c r="C33" s="8" t="n">
         <v>1258940</v>
       </c>
-      <c r="D33" s="53">
+      <c r="D33" s="56">
         <f>$C$6/C33</f>
         <v>79.43190302953278</v>
       </c>
@@ -5864,7 +5904,7 @@
         <f>'Audited Base'!$C$32</f>
         <v>1318945</v>
       </c>
-      <c r="D34" s="53">
+      <c r="D34" s="56">
         <f>$C$6/C34</f>
         <v>75.8181728578523</v>
       </c>
@@ -5925,10 +5965,10 @@
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="B6" s="54" t="n">
+      <c r="B6" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="55" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>Is FY 2025-26 a full twelve months? The company was incorporated during that year and all prior-year figures are nil.</t>
         </is>
@@ -5940,10 +5980,10 @@
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="B7" s="54" t="n">
+      <c r="B7" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="55" t="inlineStr">
+      <c r="C7" s="58" t="inlineStr">
         <is>
           <t>Why does projected rent jump from ₹8.04 lakh audited to ₹20.40 lakh?</t>
         </is>
@@ -5955,10 +5995,10 @@
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="B8" s="54" t="n">
+      <c r="B8" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="55" t="inlineStr">
+      <c r="C8" s="58" t="inlineStr">
         <is>
           <t>Why is projected staff cost ₹28.08 lakh against ₹10.08 lakh audited, for a similar roll?</t>
         </is>
@@ -5970,10 +6010,10 @@
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="B9" s="54" t="n">
+      <c r="B9" s="57" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="55" t="inlineStr">
+      <c r="C9" s="58" t="inlineStr">
         <is>
           <t>Who lent the ₹1.62 crore shown as unsecured borrowings?</t>
         </is>
@@ -5985,10 +6025,10 @@
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="B10" s="54" t="n">
+      <c r="B10" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="55" t="inlineStr">
+      <c r="C10" s="58" t="inlineStr">
         <is>
           <t>Do the projections cover Nagre Nagar alone, or both campuses?</t>
         </is>
@@ -6000,10 +6040,10 @@
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="B11" s="54" t="n">
+      <c r="B11" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="55" t="inlineStr">
+      <c r="C11" s="58" t="inlineStr">
         <is>
           <t>What are the terms of the land lease — lessor, tenure, assignment, change of control, right to create a charge?</t>
         </is>
@@ -6015,10 +6055,10 @@
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="B12" s="54" t="n">
+      <c r="B12" s="57" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="55" t="inlineStr">
+      <c r="C12" s="58" t="inlineStr">
         <is>
           <t>What is the physical capacity of the 8,500 sq ft campus?</t>
         </is>
@@ -6030,10 +6070,10 @@
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="B13" s="54" t="n">
+      <c r="B13" s="57" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="55" t="inlineStr">
+      <c r="C13" s="58" t="inlineStr">
         <is>
           <t>Confirm the entity is a Section 8 company, and what instrument can lawfully be offered.</t>
         </is>
@@ -6045,10 +6085,10 @@
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="B14" s="54" t="n">
+      <c r="B14" s="57" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="55" t="inlineStr">
+      <c r="C14" s="58" t="inlineStr">
         <is>
           <t>Is there any 12AB registration or exemption claimed?</t>
         </is>
